--- a/Savets 2026/admin/Schedule.xlsx
+++ b/Savets 2026/admin/Schedule.xlsx
@@ -1,34 +1,167 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF702E06-043A-477C-8114-302A4C9572B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6240" yWindow="2175" windowWidth="20370" windowHeight="10770"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId3"/>
+    <sheet name="Day 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Day 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+  <si>
+    <t>Men's Doubles Round 16 Match 1</t>
+  </si>
+  <si>
+    <t>Men's Doubles Quater Match 1</t>
+  </si>
+  <si>
+    <t>Men's Doubles Quater Match 2</t>
+  </si>
+  <si>
+    <t>Men's Doubles Quater Match 3</t>
+  </si>
+  <si>
+    <t>Men's Doubles Quater Match 4</t>
+  </si>
+  <si>
+    <t>Men's Doubles Semi Match 1</t>
+  </si>
+  <si>
+    <t>Men's Doubles Semi Match 2</t>
+  </si>
+  <si>
+    <t>Men's Doubles Final</t>
+  </si>
+  <si>
+    <t>Men's 40+ Group 1</t>
+  </si>
+  <si>
+    <t>Men's 40+ Group 2</t>
+  </si>
+  <si>
+    <t>Men's 40+ Group 3</t>
+  </si>
+  <si>
+    <t>Men's 40+ Group 4</t>
+  </si>
+  <si>
+    <t>Men's 40+ Group 5</t>
+  </si>
+  <si>
+    <t>Men's 40+ Group 6</t>
+  </si>
+  <si>
+    <t>Men's 50+ Group 1</t>
+  </si>
+  <si>
+    <t>Men's 50+ Group 2</t>
+  </si>
+  <si>
+    <t>Men's 50+ Group 3</t>
+  </si>
+  <si>
+    <t>Men's 50+ Group 4</t>
+  </si>
+  <si>
+    <t>Men's 50+ Group 5</t>
+  </si>
+  <si>
+    <t>Men's 40+ Round 16 Match 1</t>
+  </si>
+  <si>
+    <t>Men's 40+ Round 16 Match 2</t>
+  </si>
+  <si>
+    <t>Men's 40+ Round 16 Match 3</t>
+  </si>
+  <si>
+    <t>Men's 40+ Round 16 Match 4</t>
+  </si>
+  <si>
+    <t>Men's 40+ Quater Match 1</t>
+  </si>
+  <si>
+    <t>Men's 40+ Quater Match 2</t>
+  </si>
+  <si>
+    <t>Men's 40+ Quater Match 3</t>
+  </si>
+  <si>
+    <t>Men's 40+ Quater Match 4</t>
+  </si>
+  <si>
+    <t>Men's 40+ Semi Match 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Men's 40+ Final </t>
+  </si>
+  <si>
+    <t>Men's 40+ Semi Match 2</t>
+  </si>
+  <si>
+    <t>Men's 50+ Round 16 Match 1</t>
+  </si>
+  <si>
+    <t>Men's 50+ Round 16 Match 2</t>
+  </si>
+  <si>
+    <t>Men's 50+ Quater Match 1</t>
+  </si>
+  <si>
+    <t>Men's 50+ Quater Match 2</t>
+  </si>
+  <si>
+    <t>Men's 50+ Quater Match 3</t>
+  </si>
+  <si>
+    <t>Men's 50+ Quater Match 4</t>
+  </si>
+  <si>
+    <t>Men's 50+ Semi Match 1</t>
+  </si>
+  <si>
+    <t>Men's 50+ Final</t>
+  </si>
+  <si>
+    <t>Men's 50+ Semi Match 2</t>
+  </si>
+  <si>
+    <t>Men's 60+ Group 1</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -392,16 +525,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="11" width="9.140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="9.7109375" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" s="1">
         <v>1</v>
       </c>
@@ -420,135 +554,283 @@
       <c r="G1" s="1">
         <v>6</v>
       </c>
-      <c r="H1" s="1">
+    </row>
+    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1">
+    </row>
+    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5C29DE-68C6-44DB-883A-5775D45CBE8D}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="8" width="11.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>0.3541666666678793</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>0.3958333333321207</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>0.4375</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>0.4791666666678793</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+        <v>0.52083333333212067</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>0.5208333333321207</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+        <v>0.54166666666787933</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>0.5416666666678793</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+        <v>0.5625</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>0.5625</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+        <v>0.58333333333212067</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>0.5833333333321207</v>
-      </c>
-      <c r="B10" s="1"/>
+        <v>0.60416666666787933</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>0.6041666666678793</v>
-      </c>
-      <c r="B11" s="1"/>
+        <v>0.625</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -557,9 +839,9 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>0.625</v>
+        <v>0.64583333333212067</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -570,20 +852,8 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>0.6458333333321207</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Savets 2026/admin/Schedule.xlsx
+++ b/Savets 2026/admin/Schedule.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF702E06-043A-477C-8114-302A4C9572B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A0FB98-A223-42E0-82D2-90B4D9161C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Day 1" sheetId="1" r:id="rId1"/>
@@ -708,7 +708,7 @@
     </row>
     <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
@@ -742,7 +742,7 @@
     </row>
     <row r="6" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>0.52083333333212067</v>
+        <v>0.52083333333333304</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>23</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="7" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>0.54166666666787933</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>32</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>0.58333333333212067</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>36</v>
@@ -813,7 +813,7 @@
     </row>
     <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>0.60416666666787933</v>
+        <v>0.60416666666666696</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>28</v>
@@ -840,9 +840,6 @@
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>0.64583333333212067</v>
-      </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>

--- a/Savets 2026/admin/Schedule.xlsx
+++ b/Savets 2026/admin/Schedule.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A0FB98-A223-42E0-82D2-90B4D9161C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA407321-E909-48FE-B71B-BFCB3277595C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
   <si>
     <t>Men's Doubles Round 16 Match 1</t>
   </si>
@@ -136,6 +136,18 @@
   </si>
   <si>
     <t>Men's 60+ Group 1</t>
+  </si>
+  <si>
+    <t>Men's 60+ Group 2</t>
+  </si>
+  <si>
+    <t>Men's 60+ Semi Match 1</t>
+  </si>
+  <si>
+    <t>Men's 60+ Semi Match 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Men's 60+ Final </t>
   </si>
 </sst>
 </file>
@@ -688,7 +700,7 @@
     </row>
     <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>0.41666666666666669</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>14</v>
@@ -708,7 +720,7 @@
     </row>
     <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>0.47916666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
@@ -725,45 +737,47 @@
       <c r="F4" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>0.5</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="G5" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>0.52083333333333304</v>
+        <v>0.5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="1"/>
+        <v>31</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>0.54166666666666696</v>
+        <v>0.52083333333333304</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>32</v>
@@ -776,9 +790,6 @@
       </c>
       <c r="E7" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -786,7 +797,7 @@
     </row>
     <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>0.5625</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>27</v>
@@ -794,12 +805,18 @@
       <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>0.58333333333333304</v>
+        <v>0.5625</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>36</v>
@@ -813,12 +830,14 @@
     </row>
     <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>0.60416666666666696</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -826,7 +845,7 @@
     </row>
     <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>0.625</v>
+        <v>0.60416666666666696</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>37</v>
